--- a/SOEN 341 sprint 4.xlsx
+++ b/SOEN 341 sprint 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveconcordia-my.sharepoint.com/personal/l_yalan_live_concordia_ca/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zombi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{740FA80F-C125-40B2-8439-B5A627131025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F98648-2952-44F8-9B71-B330F3DC8287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="21225" windowHeight="14595" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="357">
   <si>
     <t>Meal-Prep SPRINT PLAN</t>
   </si>
@@ -1253,6 +1253,36 @@
   </si>
   <si>
     <t>Create an MVC style file architecture, frontend scripts, CSS, and images should be under the public folder, under source we should have our database code, backend code and html code</t>
+  </si>
+  <si>
+    <t>UT 17</t>
+  </si>
+  <si>
+    <t>UT 17.1</t>
+  </si>
+  <si>
+    <t>Understand the code</t>
+  </si>
+  <si>
+    <t>UT 17..2</t>
+  </si>
+  <si>
+    <t>Verify readability, maintainability and functionality</t>
+  </si>
+  <si>
+    <t>Security check and Error handling</t>
+  </si>
+  <si>
+    <t>Review the current module/component code to understand logic flow and dependencies.Identify sections with poor readability, duplicated logic, or weak structure.</t>
+  </si>
+  <si>
+    <t>Refactor variable names, functions, and file organization to improve maintainability.
+Run a static analysis tool and document issues detected.
+Fix at least 5 bugs or code quality issues reported by the analysis tool.</t>
+  </si>
+  <si>
+    <t>Check security-sensitive areas such as authentication flow, form validation, and user input handling.
+Write/update unit tests for the modified code.</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1497,6 +1527,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1729,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2022,6 +2058,18 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2037,38 +2085,29 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2309,7 +2348,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="2:4" ht="25.5">
+    <row r="4" spans="2:4" ht="26.25">
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
@@ -2326,7 +2365,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="2:4" ht="18">
+    <row r="7" spans="2:4" ht="17.25">
       <c r="B7" s="1"/>
       <c r="C7" s="4" t="s">
         <v>1</v>
@@ -2429,7 +2468,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:18" ht="27.75">
+    <row r="2" spans="1:18" ht="30">
       <c r="A2" s="38" t="s">
         <v>8</v>
       </c>
@@ -2849,104 +2888,104 @@
       <c r="K15" s="49"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="120" t="s">
+      <c r="B16" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="121">
+      <c r="D16" s="123">
         <v>8</v>
       </c>
-      <c r="E16" s="121" t="s">
+      <c r="E16" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="121" t="s">
+      <c r="F16" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="120">
+      <c r="G16" s="122">
         <v>6</v>
       </c>
-      <c r="H16" s="120" t="s">
+      <c r="H16" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="121" t="s">
+      <c r="I16" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="J16" s="120" t="s">
+      <c r="J16" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="K16" s="119">
+      <c r="K16" s="124">
         <v>46080</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="120"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
+      <c r="A17" s="122"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="123"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="122"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="120"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
+      <c r="A18" s="122"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="120"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="120"/>
+      <c r="A19" s="122"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="122"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A20" s="120"/>
-      <c r="B20" s="120"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="121"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="120"/>
+      <c r="A20" s="122"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="122"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="120"/>
-      <c r="B21" s="120"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="120"/>
+      <c r="A21" s="122"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="122"/>
+      <c r="K21" s="122"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="G22">
@@ -2958,51 +2997,51 @@
       <c r="A23" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="124" t="s">
+      <c r="B23" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="123" t="s">
+      <c r="C23" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="122" t="s">
+      <c r="E23" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="122" t="s">
+      <c r="F23" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="122" t="s">
+      <c r="G23" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="122" t="s">
+      <c r="H23" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="123" t="s">
+      <c r="I23" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="J23" s="122" t="s">
+      <c r="J23" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="K23" s="122" t="s">
+      <c r="K23" s="119" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="75"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="122"/>
-    </row>
-    <row r="25" spans="1:11" ht="61.5">
+      <c r="B24" s="121"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+    </row>
+    <row r="25" spans="1:11" ht="76.5">
       <c r="A25" s="86" t="s">
         <v>89</v>
       </c>
@@ -3037,7 +3076,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="183.75">
+    <row r="26" spans="1:11" ht="204">
       <c r="A26" s="86" t="s">
         <v>97</v>
       </c>
@@ -3072,7 +3111,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="123">
+    <row r="27" spans="1:11" ht="140.25">
       <c r="A27" s="87" t="s">
         <v>105</v>
       </c>
@@ -3107,7 +3146,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="61.5">
+    <row r="28" spans="1:11" ht="63.75">
       <c r="A28" s="86" t="s">
         <v>112</v>
       </c>
@@ -3142,7 +3181,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25">
+    <row r="29" spans="1:11" ht="12.75">
       <c r="A29" s="86"/>
       <c r="B29" s="86"/>
       <c r="C29" s="98"/>
@@ -3158,7 +3197,7 @@
       <c r="J29" s="91"/>
       <c r="K29" s="99"/>
     </row>
-    <row r="30" spans="1:11" ht="14.25">
+    <row r="30" spans="1:11" ht="12.75">
       <c r="A30" s="83"/>
       <c r="B30" s="83"/>
       <c r="C30" s="100"/>
@@ -3171,7 +3210,7 @@
       <c r="J30" s="83"/>
       <c r="K30" s="83"/>
     </row>
-    <row r="31" spans="1:11" ht="14.25">
+    <row r="31" spans="1:11" ht="12.75">
       <c r="A31" s="83"/>
       <c r="B31" s="83"/>
       <c r="C31" s="100"/>
@@ -3186,29 +3225,29 @@
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1">
       <c r="A32" s="75"/>
-      <c r="B32" s="124"/>
-      <c r="C32" s="123"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="123"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="122"/>
-    </row>
-    <row r="33" spans="1:11" ht="15">
+      <c r="B32" s="121"/>
+      <c r="C32" s="120"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="75"/>
-      <c r="B33" s="124"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="122"/>
-      <c r="G33" s="122"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="122"/>
-      <c r="K33" s="122"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="120"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="119"/>
     </row>
     <row r="34" spans="1:11" ht="61.5" customHeight="1">
       <c r="A34" s="86" t="s">
@@ -3341,37 +3380,37 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="K32:K33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="I16:I21"/>
-    <mergeCell ref="J16:J21"/>
     <mergeCell ref="K16:K21"/>
     <mergeCell ref="C16:C21"/>
     <mergeCell ref="D16:D21"/>
     <mergeCell ref="E16:E21"/>
     <mergeCell ref="F16:F21"/>
     <mergeCell ref="G16:G21"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="H16:H21"/>
+    <mergeCell ref="I16:I21"/>
+    <mergeCell ref="J16:J21"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K32:K33"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
@@ -3402,53 +3441,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
     </row>
     <row r="2" spans="1:9" ht="14.45" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
     </row>
     <row r="3" spans="1:9" ht="27.4" customHeight="1">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="112" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:9" ht="14.45" customHeight="1">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
     </row>
     <row r="6" spans="1:9" s="31" customFormat="1" ht="40.5" customHeight="1">
       <c r="A6" s="23" t="s">
@@ -3473,7 +3512,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="13.5">
+    <row r="7" spans="1:9" ht="14.25">
       <c r="A7" s="25" t="s">
         <v>150</v>
       </c>
@@ -3511,7 +3550,7 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
     </row>
-    <row r="9" spans="1:9" ht="27">
+    <row r="9" spans="1:9" ht="29.25">
       <c r="A9" s="25"/>
       <c r="B9" s="25" t="s">
         <v>159</v>
@@ -3528,7 +3567,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" spans="1:9" ht="27">
+    <row r="10" spans="1:9" ht="29.25">
       <c r="A10" s="25"/>
       <c r="B10" s="25" t="s">
         <v>162</v>
@@ -3547,7 +3586,7 @@
       </c>
       <c r="G10" s="102"/>
     </row>
-    <row r="11" spans="1:9" ht="27">
+    <row r="11" spans="1:9" ht="29.25">
       <c r="A11" s="25" t="s">
         <v>165</v>
       </c>
@@ -3569,7 +3608,7 @@
       <c r="G11" s="25"/>
       <c r="I11" s="32"/>
     </row>
-    <row r="12" spans="1:9" ht="39.75">
+    <row r="12" spans="1:9" ht="43.5">
       <c r="A12" s="25" t="s">
         <v>169</v>
       </c>
@@ -3591,7 +3630,7 @@
       <c r="G12" s="25"/>
       <c r="I12" s="32"/>
     </row>
-    <row r="13" spans="1:9" ht="26.25">
+    <row r="13" spans="1:9" ht="28.5">
       <c r="A13" s="25"/>
       <c r="B13" s="25" t="s">
         <v>173</v>
@@ -3610,7 +3649,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" spans="1:9" ht="26.25">
+    <row r="14" spans="1:9" ht="28.5">
       <c r="A14" s="25"/>
       <c r="B14" s="25" t="s">
         <v>176</v>
@@ -3629,7 +3668,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" spans="1:9" ht="26.25">
+    <row r="15" spans="1:9" ht="28.5">
       <c r="A15" s="25"/>
       <c r="B15" s="25" t="s">
         <v>179</v>
@@ -3648,7 +3687,7 @@
       </c>
       <c r="G15" s="104"/>
     </row>
-    <row r="16" spans="1:9" ht="27.75">
+    <row r="16" spans="1:9" ht="45">
       <c r="A16" s="25" t="s">
         <v>183</v>
       </c>
@@ -3669,7 +3708,7 @@
       </c>
       <c r="G16" s="28"/>
     </row>
-    <row r="17" spans="1:7" ht="27.75">
+    <row r="17" spans="1:7" ht="30">
       <c r="A17" s="25"/>
       <c r="B17" s="25" t="s">
         <v>187</v>
@@ -3688,7 +3727,7 @@
       </c>
       <c r="G17" s="28"/>
     </row>
-    <row r="18" spans="1:7" ht="54.75">
+    <row r="18" spans="1:7" ht="75">
       <c r="A18" s="25"/>
       <c r="B18" s="25" t="s">
         <v>190</v>
@@ -3707,7 +3746,7 @@
       </c>
       <c r="G18" s="28"/>
     </row>
-    <row r="19" spans="1:7" ht="68.25">
+    <row r="19" spans="1:7" ht="90">
       <c r="A19" s="25"/>
       <c r="B19" s="25" t="s">
         <v>193</v>
@@ -3726,7 +3765,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5">
+    <row r="20" spans="1:7" ht="14.25">
       <c r="A20" s="104"/>
       <c r="B20" s="104"/>
       <c r="C20" s="104"/>
@@ -3735,7 +3774,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5">
+    <row r="21" spans="1:7" ht="14.25">
       <c r="A21" s="25"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -3813,7 +3852,7 @@
     <col min="8" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8">
       <c r="A1" s="22"/>
       <c r="B1" s="15" t="s">
         <v>198</v>
@@ -3837,7 +3876,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24">
+    <row r="2" spans="1:8" ht="25.5">
       <c r="A2" s="16" t="s">
         <v>203</v>
       </c>
@@ -3863,7 +3902,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24">
+    <row r="3" spans="1:8" ht="25.5">
       <c r="A3" s="16" t="s">
         <v>203</v>
       </c>
@@ -3913,7 +3952,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="24">
+    <row r="5" spans="1:8" ht="25.5">
       <c r="A5" s="16" t="s">
         <v>211</v>
       </c>
@@ -3963,7 +4002,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="24">
+    <row r="7" spans="1:8" ht="25.5">
       <c r="A7" s="16" t="s">
         <v>221</v>
       </c>
@@ -4019,53 +4058,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
     </row>
     <row r="2" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="27.4" customHeight="1">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="83.25" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
     </row>
     <row r="6" spans="1:10" s="31" customFormat="1" ht="40.5" customHeight="1">
       <c r="A6" s="51" t="s">
@@ -4090,7 +4129,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="49.5">
+    <row r="7" spans="1:10" ht="51">
       <c r="A7" s="58" t="s">
         <v>65</v>
       </c>
@@ -4111,7 +4150,7 @@
       </c>
       <c r="G7" s="50"/>
     </row>
-    <row r="8" spans="1:10" ht="37.5">
+    <row r="8" spans="1:10" ht="38.25">
       <c r="A8" s="60"/>
       <c r="B8" s="61" t="s">
         <v>231</v>
@@ -4149,7 +4188,7 @@
       </c>
       <c r="G9" s="50"/>
     </row>
-    <row r="10" spans="1:10" ht="37.5">
+    <row r="10" spans="1:10" ht="51">
       <c r="A10" s="64"/>
       <c r="B10" s="60" t="s">
         <v>237</v>
@@ -4168,7 +4207,7 @@
       </c>
       <c r="G10" s="50"/>
     </row>
-    <row r="11" spans="1:10" ht="25.5">
+    <row r="11" spans="1:10" ht="26.25">
       <c r="A11" s="50"/>
       <c r="B11" s="50" t="s">
         <v>240</v>
@@ -4188,7 +4227,7 @@
       <c r="G11" s="50"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10" ht="26.25">
       <c r="A12" s="66"/>
       <c r="B12" s="67" t="s">
         <v>243</v>
@@ -4208,7 +4247,7 @@
       <c r="G12" s="50"/>
       <c r="H12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="25.5">
+    <row r="13" spans="1:10" ht="26.25">
       <c r="A13" s="66"/>
       <c r="B13" s="67" t="s">
         <v>246</v>
@@ -4286,7 +4325,7 @@
       </c>
       <c r="G16" s="50"/>
     </row>
-    <row r="17" spans="1:7" ht="37.5">
+    <row r="17" spans="1:7" ht="38.25">
       <c r="A17" s="54"/>
       <c r="B17" s="68" t="s">
         <v>259</v>
@@ -4305,7 +4344,7 @@
       </c>
       <c r="G17" s="50"/>
     </row>
-    <row r="18" spans="1:7" ht="14.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="54" t="s">
         <v>77</v>
       </c>
@@ -4347,7 +4386,7 @@
       </c>
       <c r="G19" s="50"/>
     </row>
-    <row r="20" spans="1:7" ht="37.5">
+    <row r="20" spans="1:7" ht="38.25">
       <c r="A20" s="50"/>
       <c r="B20" s="68" t="s">
         <v>267</v>
@@ -4366,7 +4405,7 @@
       </c>
       <c r="G20" s="50"/>
     </row>
-    <row r="21" spans="1:7" ht="14.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="71"/>
       <c r="B21" s="67"/>
       <c r="C21" s="50"/>
@@ -4378,7 +4417,7 @@
       <c r="F21" s="50"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:7" ht="14.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="50"/>
       <c r="B22" s="67"/>
       <c r="C22" s="50"/>
@@ -4387,7 +4426,7 @@
       <c r="F22" s="50"/>
       <c r="G22" s="50"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="50"/>
       <c r="B23" s="68"/>
       <c r="C23" s="50"/>
@@ -4463,53 +4502,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
     </row>
     <row r="2" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="27.4" customHeight="1">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="83.25" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
     </row>
     <row r="6" spans="1:10" s="31" customFormat="1" ht="40.5" customHeight="1">
       <c r="A6" s="51" t="s">
@@ -4593,7 +4632,7 @@
       </c>
       <c r="G9" s="50"/>
     </row>
-    <row r="10" spans="1:10" ht="61.5">
+    <row r="10" spans="1:10" ht="63.75">
       <c r="A10" s="66" t="s">
         <v>280</v>
       </c>
@@ -4654,7 +4693,7 @@
       <c r="G12" s="50"/>
       <c r="H12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="37.5">
+    <row r="13" spans="1:10" ht="39">
       <c r="A13" s="66"/>
       <c r="B13" s="68" t="s">
         <v>290</v>
@@ -4674,7 +4713,7 @@
       <c r="G13" s="50"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="37.5">
+    <row r="14" spans="1:10" ht="38.25">
       <c r="A14" s="60"/>
       <c r="B14" s="61" t="s">
         <v>293</v>
@@ -4773,7 +4812,7 @@
       </c>
       <c r="G18" s="50"/>
     </row>
-    <row r="19" spans="1:7" ht="25.5">
+    <row r="19" spans="1:7" ht="38.25">
       <c r="A19" s="66" t="s">
         <v>112</v>
       </c>
@@ -4794,7 +4833,7 @@
       </c>
       <c r="G19" s="50"/>
     </row>
-    <row r="20" spans="1:7" ht="25.5">
+    <row r="20" spans="1:7" ht="38.25">
       <c r="A20" s="50"/>
       <c r="B20" s="68" t="s">
         <v>312</v>
@@ -4832,7 +4871,7 @@
       </c>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:7" ht="37.5">
+    <row r="22" spans="1:7" ht="38.25">
       <c r="A22" s="71"/>
       <c r="B22" s="67" t="s">
         <v>318</v>
@@ -4870,7 +4909,7 @@
       </c>
       <c r="G23" s="50"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="50"/>
       <c r="B24" s="68"/>
       <c r="C24" s="50"/>
@@ -4949,53 +4988,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
     </row>
     <row r="2" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A2" s="116"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="A2" s="111"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="27.4" customHeight="1">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="112" t="s">
         <v>227</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="83.25" customHeight="1">
-      <c r="A4" s="118"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
+      <c r="A5" s="111"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
     </row>
     <row r="6" spans="1:10" s="31" customFormat="1" ht="40.5" customHeight="1">
       <c r="A6" s="51" t="s">
@@ -5041,7 +5080,7 @@
       </c>
       <c r="G7" s="50"/>
     </row>
-    <row r="8" spans="1:10" ht="37.5">
+    <row r="8" spans="1:10" ht="38.25">
       <c r="A8" s="60"/>
       <c r="B8" s="61" t="s">
         <v>328</v>
@@ -5164,16 +5203,16 @@
       <c r="A15" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="114" t="s">
         <v>345</v>
       </c>
-      <c r="C15" s="112" t="s">
+      <c r="C15" s="116" t="s">
         <v>346</v>
       </c>
       <c r="D15" s="108" t="s">
         <v>347</v>
       </c>
-      <c r="E15" s="114">
+      <c r="E15" s="118">
         <v>3</v>
       </c>
       <c r="F15" s="108" t="s">
@@ -5183,10 +5222,10 @@
     </row>
     <row r="16" spans="1:10" ht="44.25" customHeight="1">
       <c r="A16" s="109"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="113"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="109"/>
-      <c r="E16" s="113"/>
+      <c r="E16" s="117"/>
       <c r="F16" s="109"/>
       <c r="G16" s="109"/>
       <c r="J16" s="47"/>
@@ -5200,46 +5239,70 @@
       <c r="F17" s="50"/>
       <c r="G17" s="50"/>
     </row>
-    <row r="18" spans="1:7" ht="14.25">
-      <c r="A18" s="66"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="65">
-        <f>SUM(E7:E12)</f>
-        <v>29.5</v>
+    <row r="18" spans="1:7" ht="51">
+      <c r="A18" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
       </c>
       <c r="F18" s="50"/>
       <c r="G18" s="50"/>
     </row>
-    <row r="19" spans="1:7" ht="14.25">
+    <row r="19" spans="1:7" ht="76.5">
       <c r="A19" s="66"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="50"/>
+      <c r="B19" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3</v>
+      </c>
       <c r="F19" s="50"/>
       <c r="G19" s="50"/>
     </row>
-    <row r="20" spans="1:7" ht="14.25">
+    <row r="20" spans="1:7" ht="38.25">
       <c r="A20" s="50"/>
       <c r="B20" s="68"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="65"/>
+      <c r="C20" s="65" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="126" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
       <c r="F20" s="50"/>
       <c r="G20" s="50"/>
     </row>
-    <row r="21" spans="1:7" ht="14.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="50"/>
       <c r="B21" s="68"/>
       <c r="C21" s="50"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="50"/>
+      <c r="E21" s="65">
+        <f>SUM(E7:E20)</f>
+        <v>39.5</v>
+      </c>
       <c r="F21" s="50"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:7" ht="14.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="71"/>
       <c r="B22" s="67"/>
       <c r="C22" s="50"/>
@@ -5248,7 +5311,7 @@
       <c r="F22" s="50"/>
       <c r="G22" s="50"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="50"/>
       <c r="B23" s="67"/>
       <c r="C23" s="50"/>
@@ -5257,7 +5320,7 @@
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="50"/>
       <c r="B24" s="68"/>
       <c r="C24" s="50"/>
